--- a/Result/profitability/5864.xlsx
+++ b/Result/profitability/5864.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
         <v>1.66</v>
       </c>
       <c r="M2" t="n">
-        <v>0.88875</v>
+        <v>1.72375</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -760,7 +760,7 @@
         <v>-2.42</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5800000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -869,11 +869,11 @@
         <v>0.76</v>
       </c>
       <c r="M4" t="n">
-        <v>0.73375</v>
+        <v>1.72125</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0.86</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9875</v>
+        <v>1.7475</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1089,7 +1089,7 @@
         <v>-0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.90125</v>
+        <v>1.5425</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1208,11 +1208,11 @@
         <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8699999999999999</v>
+        <v>1.5375</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -7163,6 +7163,125 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>5864</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>3520</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>99.27</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3382</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>96.07%</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="n">
+        <v>3410</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3395</v>
+      </c>
+      <c r="L58" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.5225</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W58" t="n">
+        <v>3.330000000000001</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0.9794117647058824</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.3399999999999892</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.003436773476195087</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>9.353846153846154</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0.4699999999999989</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.004757085020242968</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK58" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
